--- a/example-zh-cn.xlsx
+++ b/example-zh-cn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chatgpt\rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9290CCC-40F5-6F4F-B1BB-3AB7C8D11D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C777B6-D83D-4F64-9588-B1035BBDED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16860" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
   <sheets>
     <sheet name="设备列表" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>设备名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,10 +166,6 @@
   </si>
   <si>
     <t>机柜1</t>
-  </si>
-  <si>
-    <t>http://rack.szqp.site</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机柜图生成器</t>
@@ -514,6 +510,60 @@
       <t xml:space="preserve">“Sheet中红色内容为样例，可以删除，但需要保留第一列表头，且表头名称不能修改。
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM SAN-B24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAN交换机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78H1235</t>
+  </si>
+  <si>
+    <t>78H1236</t>
+  </si>
+  <si>
+    <t>78H1237</t>
+  </si>
+  <si>
+    <t>78H1238</t>
+  </si>
+  <si>
+    <t>78H1239</t>
+  </si>
+  <si>
+    <t>78H1240</t>
+  </si>
+  <si>
+    <t>78H1241</t>
+  </si>
+  <si>
+    <t>78H1242</t>
+  </si>
+  <si>
+    <t>78H1243</t>
+  </si>
+  <si>
+    <t>78H1244</t>
+  </si>
+  <si>
+    <t>IPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWAYA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rack-web.szqp.site</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +571,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -699,6 +749,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -713,18 +775,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1062,17 +1112,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D994C1D-E910-5148-8DBD-CEDB986AF5A3}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="11" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="11"/>
-    <col min="8" max="8" width="41.83203125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="6"/>
+    <col min="8" max="8" width="41.875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1088,17 +1138,17 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1112,19 +1162,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="9">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="4">
         <v>123456</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1140,17 +1190,17 @@
       <c r="E3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1166,11 +1216,15 @@
       <c r="E4" s="2">
         <v>11</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1186,17 +1240,17 @@
       <c r="E5" s="2">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1212,11 +1266,15 @@
       <c r="E6" s="2">
         <v>22</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1232,11 +1290,13 @@
       <c r="E7" s="2">
         <v>35</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1252,11 +1312,13 @@
       <c r="E8" s="2">
         <v>42</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1272,11 +1334,13 @@
       <c r="E9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1292,11 +1356,13 @@
       <c r="E10" s="2">
         <v>15</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1312,11 +1378,13 @@
       <c r="E11" s="2">
         <v>42</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1332,11 +1400,13 @@
       <c r="E12" s="2">
         <v>6</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1352,11 +1422,13 @@
       <c r="E13" s="2">
         <v>18</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1372,13 +1444,15 @@
       <c r="E14" s="2">
         <v>12</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
@@ -1392,9 +1466,15 @@
       <c r="E15" s="2">
         <v>4</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="F15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1406,168 +1486,168 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBC7C08-94AB-6E40-82CC-9BA77B7FD227}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="71.33203125" customWidth="1"/>
+    <col min="6" max="6" width="71.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="40" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/example-zh-cn.xlsx
+++ b/example-zh-cn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chatgpt\rack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C777B6-D83D-4F64-9588-B1035BBDED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F638215E-A6F5-274E-89A7-EEA7890C854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
   <sheets>
     <sheet name="设备列表" sheetId="1" r:id="rId1"/>
@@ -571,7 +571,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -693,7 +693,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -703,6 +703,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,9 +749,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -775,6 +778,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1112,367 +1118,367 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D994C1D-E910-5148-8DBD-CEDB986AF5A3}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="6"/>
-    <col min="8" max="8" width="41.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="41.83203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>123456</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" ht="17">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>8</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>15</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>20</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>30</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>40</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>42</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>7</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>15</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>41</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>42</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>9</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>18</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>10</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>12</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1486,168 +1492,168 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBC7C08-94AB-6E40-82CC-9BA77B7FD227}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="6" max="6" width="71.375" customWidth="1"/>
+    <col min="6" max="6" width="71.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="40" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
